--- a/data_src/levels/ch1_l01/关卡配置表.xlsx
+++ b/data_src/levels/ch1_l01/关卡配置表.xlsx
@@ -773,10 +773,8 @@
           <t>Aroz组合成员 Leo，让化妆师 May购买美式咖啡，不是为了工作，而是为了给房卡。</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="D4" t="n">
+        <v>8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -793,10 +791,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H4" t="n">
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
